--- a/BOM Template.xlsx
+++ b/BOM Template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>Bill of Materials</t>
   </si>
@@ -175,13 +175,7 @@
     <t>Column=Quantity</t>
   </si>
   <si>
-    <t>Your Name</t>
-  </si>
-  <si>
-    <t>Your Signature</t>
-  </si>
-  <si>
-    <t>Your Logo</t>
+    <t>Hossein Bagheri</t>
   </si>
 </sst>
 </file>
@@ -980,6 +974,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -993,13 +994,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1595,6 +1589,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>288472</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>27215</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>360713</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>190501</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10232572" y="707572"/>
+          <a:ext cx="1122712" cy="1110343"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>351234</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>59533</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1660921</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>39590</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="351234" y="3149205"/>
+          <a:ext cx="1893093" cy="503932"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1967,9 +2054,7 @@
       <c r="F5" s="74"/>
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
-      <c r="I5" s="89" t="s">
-        <v>53</v>
-      </c>
+      <c r="I5" s="85"/>
       <c r="J5" s="24"/>
     </row>
     <row r="6" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2117,9 +2202,7 @@
     </row>
     <row r="15" spans="1:10" s="39" customFormat="1" ht="13.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="44"/>
-      <c r="B15" s="90" t="s">
-        <v>52</v>
-      </c>
+      <c r="B15" s="86"/>
       <c r="C15" s="46"/>
       <c r="D15" s="36"/>
       <c r="E15" s="36"/>
@@ -2142,10 +2225,10 @@
       <c r="J16" s="38"/>
     </row>
     <row r="17" spans="1:10" s="39" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="87" t="s">
+      <c r="A17" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="88"/>
+      <c r="B17" s="90"/>
       <c r="C17" s="46" t="s">
         <v>46</v>
       </c>
@@ -2158,10 +2241,10 @@
       <c r="J17" s="38"/>
     </row>
     <row r="18" spans="1:10" s="39" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="85" t="s">
+      <c r="A18" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="86"/>
+      <c r="B18" s="88"/>
       <c r="C18" s="47"/>
       <c r="D18" s="49"/>
       <c r="E18" s="49"/>
@@ -2241,8 +2324,9 @@
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;BAltium Limited Confidential&amp;B&amp;C&amp;D&amp;RPage &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
